--- a/education_forms/043_learning_accessibility_audit_request_form--education_forms.xlsx
+++ b/education_forms/043_learning_accessibility_audit_request_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form Id 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>accessibility_audit</t>
+          <t>accessibility audit</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>accessibility_report</t>
+          <t>accessibility report</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>accessibility_recommendation</t>
+          <t>accessibility recommendation</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>learning_materials</t>
+          <t>learning materials</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>training_teams</t>
+          <t>training teams</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>in progress</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>school_1</t>
+          <t>school 1</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>school_2</t>
+          <t>school 2</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>school_3</t>
+          <t>school 3</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>tag_goals</t>
+          <t>tag goals</t>
         </is>
       </c>
     </row>
